--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104764_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104764_W34.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4732</v>
+        <v>6.9717</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0981</v>
+        <v>5.8364</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3751</v>
+        <v>1.1352</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6532</v>
+        <v>5.0181</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1394</v>
+        <v>4.3954</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5138</v>
+        <v>0.6227</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2171</v>
+        <v>5.9609</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0682</v>
+        <v>5.1571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1489</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4361</v>
+        <v>-0.9428</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0713</v>
+        <v>-0.7617</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3648</v>
+        <v>-0.1811</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4553</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4553</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5225</v>
+        <v>-0.6399</v>
       </c>
       <c r="T2" t="n">
-        <v>1.881</v>
+        <v>-0.6692</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6415</v>
+        <v>0.0294</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1578</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5082</v>
+        <v>6.3097</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5298</v>
+        <v>3.9346</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9784</v>
+        <v>2.3751</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0181</v>
+        <v>4.6532</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3954</v>
+        <v>3.1394</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6227</v>
+        <v>1.5138</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9609</v>
+        <v>3.2171</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1571</v>
+        <v>3.0682</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9428</v>
+        <v>1.4361</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7617</v>
+        <v>0.0713</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1811</v>
+        <v>1.3648</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0487</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0487</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1033</v>
+        <v>1.359</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9758</v>
+        <v>0.7175</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1275</v>
+        <v>0.6415</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5447</v>
+        <v>-0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5573</v>
+        <v>5.1076</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9952</v>
+        <v>3.3925</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5621</v>
+        <v>1.7152</v>
       </c>
       <c r="G4" t="n">
         <v>2.4047</v>
@@ -766,13 +766,13 @@
         <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7868</v>
+        <v>1.3372</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0926</v>
+        <v>0.4899</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6942</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9614</v>
+        <v>4.5469</v>
       </c>
       <c r="E5" t="n">
-        <v>3.068</v>
+        <v>3.2771</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8934</v>
+        <v>1.2698</v>
       </c>
       <c r="G5" t="n">
         <v>4.1472</v>
@@ -844,13 +844,13 @@
         <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0418</v>
+        <v>0.6273</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1623</v>
+        <v>0.3714</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1205</v>
+        <v>0.2559</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3987</v>
+        <v>2.8551</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7488</v>
+        <v>1.1739</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6499</v>
+        <v>1.6812</v>
       </c>
       <c r="G6" t="n">
         <v>4.6795</v>
@@ -922,13 +922,13 @@
         <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0532</v>
+        <v>0.4032</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4182</v>
+        <v>0.0068</v>
       </c>
       <c r="U6" t="n">
-        <v>0.365</v>
+        <v>0.3964</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0895</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9348</v>
+        <v>1.3356</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3042</v>
+        <v>0.8304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6307</v>
+        <v>0.5052</v>
       </c>
       <c r="G7" t="n">
         <v>1.2474</v>
@@ -1000,13 +1000,13 @@
         <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4598</v>
+        <v>-0.1394</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0926</v>
+        <v>-0.3812</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3672</v>
+        <v>0.2418</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2513</v>
+        <v>0.5579</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0684</v>
+        <v>0.2382</v>
       </c>
       <c r="F8" t="n">
         <v>0.3197</v>
@@ -1078,10 +1078,10 @@
         <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1055</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9061</v>
+        <v>-0.5995</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1994</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4483</v>
+        <v>0.2903</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8721</v>
+        <v>-0.0708</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4239</v>
+        <v>0.3611</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9837</v>
@@ -1156,13 +1156,13 @@
         <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2882</v>
+        <v>1.0268</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5576</v>
+        <v>0.2437</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8458</v>
+        <v>0.7831</v>
       </c>
       <c r="V9" t="n">
         <v>1.2472</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4625</v>
+        <v>-0.1559</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0848</v>
+        <v>0.2218</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3777</v>
@@ -1234,10 +1234,10 @@
         <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3856</v>
+        <v>-0.079</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4182</v>
+        <v>-0.1116</v>
       </c>
       <c r="U10" t="n">
         <v>0.0327</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6426</v>
+        <v>-1.2663</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.265</v>
+        <v>-0.8887</v>
       </c>
       <c r="F11" t="n">
         <v>-0.3776</v>
@@ -1312,10 +1312,10 @@
         <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7385</v>
+        <v>-0.3622</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9061</v>
+        <v>-0.5298</v>
       </c>
       <c r="U11" t="n">
         <v>0.1677</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7781</v>
+        <v>-1.3773</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.706</v>
+        <v>-1.5876</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.2103</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3887</v>
@@ -1390,13 +1390,13 @@
         <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1405</v>
+        <v>-0.7398</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9061</v>
+        <v>-0.7877</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2344</v>
+        <v>0.0479</v>
       </c>
       <c r="V12" t="n">
         <v>0.1578</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8124</v>
+        <v>-1.8401</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3922</v>
+        <v>-0.6081</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4202</v>
+        <v>-1.232</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9369</v>
@@ -1468,13 +1468,13 @@
         <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1533</v>
+        <v>-0.1811</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3714</v>
+        <v>0.1555</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5248</v>
+        <v>-0.3366</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8603</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.941</v>
+        <v>23.3352</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3556</v>
+        <v>15.7497</v>
       </c>
       <c r="F14" t="n">
-        <v>7.585700000000001</v>
+        <v>7.585500000000001</v>
       </c>
       <c r="G14" t="n">
         <v>13.9418</v>
@@ -1546,13 +1546,13 @@
         <v>14.7963</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4191999999999996</v>
+        <v>1.813199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.4882</v>
+        <v>-1.0942</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9075</v>
+        <v>2.9077</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3870999999999996</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8158</v>
+        <v>2.0387</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0452</v>
+        <v>1.519</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7706</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0.8098</v>
@@ -1624,13 +1624,13 @@
         <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3718</v>
+        <v>0.5947</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4182</v>
+        <v>0.0556</v>
       </c>
       <c r="U15" t="n">
-        <v>0.79</v>
+        <v>0.5391</v>
       </c>
       <c r="V15" t="n">
         <v>1.0895</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9878</v>
+        <v>0.4848</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7916</v>
+        <v>0.8804</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8038</v>
+        <v>-0.3956</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8077</v>
+        <v>0.2908</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.1595</v>
+        <v>0.2702</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3518</v>
+        <v>0.0206</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.203</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6795</v>
+        <v>0.8306</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4764</v>
+        <v>0.1336</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6047</v>
+        <v>-0.6734</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.48</v>
+        <v>-0.5604</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1246</v>
+        <v>-0.113</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9105</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2276</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1382</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>2.111</v>
+        <v>0.1242</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0433</v>
+        <v>-0.0838</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0677</v>
+        <v>0.208</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7739</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1789</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.405</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0424</v>
+        <v>-0.6391</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4066</v>
+        <v>1.1333</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3642</v>
+        <v>-1.7724</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2908</v>
+        <v>-2.8077</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2702</v>
+        <v>-3.1595</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0206</v>
+        <v>0.3518</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9641999999999999</v>
+        <v>-1.203</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8306</v>
+        <v>-1.6795</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1336</v>
+        <v>0.4764</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6734</v>
+        <v>-1.6047</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5604</v>
+        <v>-1.48</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.113</v>
+        <v>-0.1246</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2276</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2276</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3182</v>
+        <v>0.4841</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5576</v>
+        <v>0.3851</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2394</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1578</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1578</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>B. JEFFERSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7995</v>
+        <v>-1.295</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8568</v>
+        <v>-0.4028</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0572</v>
+        <v>-0.8923</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.345</v>
+        <v>-0.553</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8781</v>
+        <v>-0.8651</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5331</v>
+        <v>0.3121</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8489</v>
+        <v>0.3362</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.335</v>
+        <v>0.0689</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1839</v>
+        <v>0.2672</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.194</v>
+        <v>-0.8891</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5431</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3492</v>
+        <v>0.0449</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3658</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9105</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7535</v>
+        <v>-1.0396</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4129</v>
+        <v>-0.7389</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3407</v>
+        <v>-0.3006</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1578</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. JEFFERSON</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6888</v>
+        <v>-1.5486</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6397</v>
+        <v>-1.449</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0491</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.553</v>
+        <v>-1.345</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8651</v>
+        <v>-2.8781</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3121</v>
+        <v>1.5331</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3362</v>
+        <v>0.8489</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0689</v>
+        <v>-0.335</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2672</v>
+        <v>1.1839</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8891</v>
+        <v>-2.194</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-2.5431</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0449</v>
+        <v>0.3492</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4553</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4553</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4333</v>
+        <v>1.0045</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9758</v>
+        <v>-0.1794</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4575</v>
+        <v>1.1839</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1578</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1302</v>
+        <v>-1.5763</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1969</v>
+        <v>0.9075</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.327</v>
+        <v>-2.4839</v>
       </c>
       <c r="G20" t="n">
         <v>0.3192</v>
@@ -2014,13 +2014,13 @@
         <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7177</v>
+        <v>-0.1639</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4267</v>
+        <v>-0.716</v>
       </c>
       <c r="U20" t="n">
-        <v>0.709</v>
+        <v>0.5521</v>
       </c>
       <c r="V20" t="n">
         <v>0.5447</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7495</v>
+        <v>-2.7809</v>
       </c>
       <c r="E21" t="n">
         <v>-2.7287</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0209</v>
+        <v>-0.0522</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6589</v>
@@ -2092,13 +2092,13 @@
         <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3182</v>
+        <v>-0.3496</v>
       </c>
       <c r="T21" t="n">
         <v>-0.5576</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2394</v>
+        <v>0.208</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. VILA</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0426</v>
+        <v>-3.0241</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8576</v>
+        <v>-1.4048</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.185</v>
+        <v>-1.6193</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4513</v>
+        <v>-1.8614</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6575</v>
+        <v>-1.5546</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7937</v>
+        <v>-0.3069</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3172</v>
+        <v>0.1749</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7379</v>
+        <v>0.4137</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5793</v>
+        <v>-0.2388</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.134</v>
+        <v>-2.0364</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9196</v>
+        <v>-1.9683</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2144</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4087</v>
+        <v>-0.0245</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4596</v>
+        <v>-0.214</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.051</v>
+        <v>0.1895</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3602</v>
+        <v>-3.4473</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0654</v>
+        <v>-0.1838</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2949</v>
+        <v>-3.2635</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8918</v>
@@ -2248,13 +2248,13 @@
         <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3091</v>
+        <v>-0.3962</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2886</v>
+        <v>-0.407</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0205</v>
+        <v>0.0108</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4764</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>E. VILA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4806</v>
+        <v>-3.6418</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6417</v>
+        <v>-2.3314</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8388</v>
+        <v>-1.3105</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8614</v>
+        <v>-3.4513</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5546</v>
+        <v>-1.6575</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3069</v>
+        <v>-1.7937</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1749</v>
+        <v>-2.3172</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4137</v>
+        <v>-0.7379</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2388</v>
+        <v>-1.5793</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0364</v>
+        <v>-1.134</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9683</v>
+        <v>-0.9196</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.2144</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3658</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2276</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.481</v>
+        <v>-0.1906</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4509</v>
+        <v>-0.0141</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0301</v>
+        <v>-0.1765</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.5358</v>
+        <v>-6.5114</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.236</v>
+        <v>-3.5253</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2997</v>
+        <v>-2.9861</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7924</v>
@@ -2404,13 +2404,13 @@
         <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4867</v>
+        <v>-0.4623</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1479</v>
+        <v>-0.4372</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3388</v>
+        <v>-0.0251</v>
       </c>
       <c r="V25" t="n">
         <v>-0.387</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.9412</v>
+        <v>-21.941</v>
       </c>
       <c r="E26" t="n">
         <v>-7.585599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.3556</v>
+        <v>-14.3557</v>
       </c>
       <c r="G26" t="n">
         <v>-13.9417</v>
@@ -2452,7 +2452,7 @@
         <v>-12.9277</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0141</v>
+        <v>-1.014100000000001</v>
       </c>
       <c r="J26" t="n">
         <v>4.1975</v>
@@ -2470,7 +2470,7 @@
         <v>-18.2476</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1085</v>
+        <v>0.1085000000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-7.9672</v>
@@ -2479,19 +2479,19 @@
         <v>-14.7961</v>
       </c>
       <c r="R26" t="n">
-        <v>6.828899999999999</v>
+        <v>6.8289</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4191999999999996</v>
+        <v>-0.4192000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.9075</v>
+        <v>-2.9073</v>
       </c>
       <c r="U26" t="n">
         <v>2.4883</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3868999999999998</v>
+        <v>0.3869000000000002</v>
       </c>
       <c r="W26" t="n">
         <v>5.920699999999999</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104764_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104764_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.920799999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104764_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.5338</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
